--- a/stories/arbres/ATOM-JEU.BAS.001-07.xlsx
+++ b/stories/arbres/ATOM-JEU.BAS.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Klara et papa sont au gymnase. Un petit panier est accroché bas. Papa donne le ballon. Papa dit : on va passer le ballon. Ensuite, chacun a un lancer. Klara passe. Papa rend. C'est le lancer de Klara. Elle lance vers le panier. Le ballon rentre. Papa a son lancer. Klara dit : chacun un lancer. Ils se passent encore le ballon.</t>
+          <t>Klara et papa sont au gymnase. Un petit panier est accroché bas. Papa donne le ballon. On va passer le ballon. Ensuite, chacun a un lancer. Klara passe. Papa rend. C'est le lancer de Klara. Elle lance vers le panier. Le ballon rentre. Papa a son lancer. Chacun un lancer. Ils se passent encore le ballon.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Klara et papa sont au gymnase. Un petit panier est accroché bas. Papa donne le ballon.
+papa|On va passer le ballon. Ensuite, chacun a un lancer.
+narrateur|Klara passe. Papa rend. C'est le lancer de Klara. Elle lance vers le panier. Le ballon rentre. Papa a son lancer.
+enfant-f|Chacun un lancer.
+narrateur|Ils se passent encore le ballon.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Klara joue au basket. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Klara a passé le ballon. Elle a visé le panier. Chacun a eu un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range le ballon. Klara essuie ses mains.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAS.001-07.xlsx
+++ b/stories/arbres/ATOM-JEU.BAS.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Ils se passent encore le ballon.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Klara joue au basket. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Klara a passé le ballon. Elle a visé le panier. Chacun a eu un lancer.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Papa range le ballon. Klara essuie ses mains.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.BAS.001-07.xlsx
+++ b/stories/arbres/ATOM-JEU.BAS.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Klara vise le panier au gymnase</t>
+          <t>Le carré de soleil au gymnase</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JEU.BAL.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un carré de soleil dort sur le plancher. Mila se passe le ballon avec papa. Chacun a un lancer vers le petit panier.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Klara et papa sont au gymnase. Un petit panier est accroché bas. Papa donne le ballon. On va passer le ballon. Ensuite, chacun a un lancer. Klara passe. Papa rend. C'est le lancer de Klara. Elle lance vers le panier. Le ballon rentre. Papa a son lancer. Chacun un lancer. Ils se passent encore le ballon.</t>
+          <t>Un carré de soleil est posé sur le plancher. La poussière y danse, toute lente. Un gilet rouge est plié sur le banc. Il sent la lessive. L'horloge fait un tout petit tic. Tu vois le carré, Mila ? Il est chaud. Papa pose la paume dessus. Oui. Il est tiède. Les hautes fenêtres sont claires. Une mouche va, puis revient. Mila pose le pied dans le carré. Il est tiède sous le pied. Le soleil l'a posé là. En ce moment, Mila est au gymnase. Un petit panier est accroché bas. Le filet blanc pend, tout doux. Papa ouvre le sac. Le ballon orange en sort. Il roule jusqu'au carré de soleil. Il brille. Il est tout orange, papa. Oui. On va passer le ballon. Ensuite, chacun a un lancer. Mila prend le ballon. Il est lisse sous les doigts. Tu me le passes ? Mila passe le ballon. Papa le reçoit. Bravo. Tu as passé. Papa rend le ballon. C'est ton lancer, Mila. Mila regarde le panier. Elle lance vers le panier. Le ballon touche le filet. Il rentre. Dedans ! Bravo, Mila. Tu as visé le panier. Chacun a un lancer. À moi maintenant. Papa lance. Le ballon rentre. Chacun un lancer. Oui. On se passe encore le ballon. Mila passe. Papa passe. Le plancher sonne un peu. Le gilet rouge reste sur le banc. Mila attend son lancer. Elle lance vers le panier. Le ballon rentre encore. Bravo. Tu as passé. Tu as visé. Chacun a eu un lancer. Le carré de soleil a bougé un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1329,74 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Klara et papa sont au gymnase. Un petit panier est accroché bas. Papa donne le ballon.
-papa|On va passer le ballon. Ensuite, chacun a un lancer.
-narrateur|Klara passe. Papa rend. C'est le lancer de Klara. Elle lance vers le panier. Le ballon rentre. Papa a son lancer.
+          <t>narrateur|Un carré de soleil est posé sur le plancher.
+narrateur|La poussière y danse, toute lente.
+narrateur|Un gilet rouge est plié sur le banc.
+narrateur|Il sent la lessive.
+narrateur|L'horloge fait un tout petit tic.
+papa|Tu vois le carré, Mila ?
+enfant-f|Il est chaud.
+narrateur|Papa pose la paume dessus.
+papa|Oui.
+papa|Il est tiède.
+narrateur|Les hautes fenêtres sont claires.
+narrateur|Une mouche va, puis revient.
+narrateur|Mila pose le pied dans le carré.
+enfant-f|Il est tiède sous le pied.
+papa|Le soleil l'a posé là.
+narrateur|En ce moment, Mila est au gymnase.
+narrateur|Un petit panier est accroché bas.
+narrateur|Le filet blanc pend, tout doux.
+narrateur|Papa ouvre le sac.
+narrateur|Le ballon orange en sort.
+narrateur|Il roule jusqu'au carré de soleil.
+narrateur|Il brille.
+enfant-f|Il est tout orange, papa.
+papa|Oui.
+papa|On va passer le ballon.
+papa|Ensuite, chacun a un lancer.
+narrateur|Mila prend le ballon.
+narrateur|Il est lisse sous les doigts.
+papa|Tu me le passes ?
+narrateur|Mila passe le ballon.
+narrateur|Papa le reçoit.
+papa|Bravo.
+papa|Tu as passé.
+narrateur|Papa rend le ballon.
+papa|C'est ton lancer, Mila.
+narrateur|Mila regarde le panier.
+narrateur|Elle lance vers le panier.
+narrateur|Le ballon touche le filet.
+narrateur|Il rentre.
+enfant-f|Dedans !
+papa|Bravo, Mila.
+papa|Tu as visé le panier.
+papa|Chacun a un lancer.
+papa|À moi maintenant.
+narrateur|Papa lance.
+narrateur|Le ballon rentre.
 enfant-f|Chacun un lancer.
-narrateur|Ils se passent encore le ballon.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Oui.
+papa|On se passe encore le ballon.
+narrateur|Mila passe.
+narrateur|Papa passe.
+narrateur|Le plancher sonne un peu.
+narrateur|Le gilet rouge reste sur le banc.
+narrateur|Mila attend son lancer.
+narrateur|Elle lance vers le panier.
+narrateur|Le ballon rentre encore.
+papa|Bravo.
+papa|Tu as passé.
+papa|Tu as visé.
+papa|Chacun a eu un lancer.
+narrateur|Le carré de soleil a bougé un peu.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>ballon,horloge</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1421,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Klara joue au basket. Que fait-elle ?</t>
+          <t>Mila joue au basket. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1577,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Klara joue au basket. Que fait-elle ?</t>
+          <t>narrateur|Mila joue au basket.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Klara a passé le ballon. Elle a visé le panier. Chacun a eu un lancer.</t>
+          <t>Mila a passé le ballon. Elle a visé le panier. Chacun a eu un lancer. Tu as passé, Mila. Bravo. Tu as visé le panier. Chacun un lancer. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1750,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Klara a passé le ballon. Elle a visé le panier. Chacun a eu un lancer.</t>
+          <t>narrateur|Mila a passé le ballon.
+narrateur|Elle a visé le panier.
+narrateur|Chacun a eu un lancer.
+papa|Tu as passé, Mila.
+papa|Bravo.
+papa|Tu as visé le panier.
+enfant-f|Chacun un lancer.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1785,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le ballon. Klara essuie ses mains.</t>
+          <t>Papa range le ballon. Mila essuie ses mains sur son pantalon. Le gilet rouge est encore sur le banc. Tu le prends ? Mila le prend. Il est doux. Tu bois une gorgée ? Oui. L'eau sent un peu le plastique. On a visé le panier. Oui, papa. On s'est passé le ballon. Chacun a eu un lancer. Bravo, ma grande. Tu as fait du bon travail. Le carré de soleil est plus petit. L'horloge fait encore tic.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,10 +1925,30 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range le ballon. Klara essuie ses mains.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Papa range le ballon.
+narrateur|Mila essuie ses mains sur son pantalon.
+narrateur|Le gilet rouge est encore sur le banc.
+papa|Tu le prends ?
+narrateur|Mila le prend.
+enfant-f|Il est doux.
+papa|Tu bois une gorgée ?
+enfant-f|Oui.
+enfant-f|L'eau sent un peu le plastique.
+papa|On a visé le panier.
+enfant-f|Oui, papa.
+enfant-f|On s'est passé le ballon.
+papa|Chacun a eu un lancer.
+papa|Bravo, ma grande.
+papa|Tu as fait du bon travail.
+narrateur|Le carré de soleil est plus petit.
+narrateur|L'horloge fait encore tic.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>horloge</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,7 +1973,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le gilet rouge est sur les épaules de Mila. J'ai passé. J'ai visé le panier. Bravo, Mila. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2113,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le gilet rouge est sur les épaules de Mila.
+enfant-f|J'ai passé.
+enfant-f|J'ai visé le panier.
+papa|Bravo, Mila.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2177,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAS.001-07.xlsx
+++ b/stories/arbres/ATOM-JEU.BAS.001-07.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Klara et papa sont au gymnase. Un petit &lt;emphasis level="moderate"&gt;panier&lt;/emphasis&gt; est accroché bas. Papa donne le ballon. Papa dit : on va passer le ballon. Ensuite, chacun a un lancer. Klara passe. Papa rend. C'est le lancer de Klara. Elle lance vers le panier. Le ballon rentre. Papa a son lancer. Klara dit : chacun un lancer. Ils se passent encore le ballon.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un carré de soleil est posé sur le plancher. La poussière y danse, toute lente. Un gilet rouge est plié sur le banc. Il sent la lessive. L'horloge fait un tout petit tic. Tu vois le carré, Mila ? Il est chaud. Papa pose la paume dessus. Oui. Il est tiède. Les hautes fenêtres sont claires. Une mouche va, puis revient. Mila pose le pied dans le carré. Il est tiède sous le pied. Le soleil l'a posé là. En ce moment, Mila est au gymnase. Un petit panier est accroché bas. Le filet blanc pend, tout doux. Papa ouvre le sac. Le ballon orange en sort. Il roule jusqu'au carré de soleil. Il brille. Il est tout orange, papa. Oui. On va passer le ballon. Ensuite, chacun a un lancer. Mila prend le ballon. Il est lisse sous les doigts. Tu me le passes ? Mila passe le ballon. Papa le reçoit. Bravo. Tu as passé. Papa rend le ballon. C'est ton lancer, Mila. Mila regarde le panier. Elle lance vers le panier. Le ballon touche le filet. Il rentre. Dedans ! Bravo, Mila. Tu as visé le panier. Chacun a un lancer. À moi maintenant. Papa lance. Le ballon rentre. Chacun un lancer. Oui. On se passe encore le ballon. Mila passe. Papa passe. Le plancher sonne un peu. Le gilet rouge reste sur le banc. Mila attend son lancer. Elle lance vers le panier. Le ballon rentre encore. Bravo. Tu as passé. Tu as visé. Chacun a eu un lancer. Le carré de soleil a bougé un peu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Klara joue au basket. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila joue au basket. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1581,7 +1581,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1606,12 +1605,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a passé le ballon. Elle a visé le panier. Chacun a eu un lancer. Tu as passé, Mila. Bravo. Tu as visé le panier. Chacun un lancer. C'est du bon travail.</t>
+          <t>Mila a passé le ballon. Elle a visé le panier. Chacun a eu un lancer. Tu as passé, Mila. Bravo. Tu as visé le panier. Chacun un lancer.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Klara a passé le ballon. Elle a visé le &lt;emphasis level="moderate"&gt;panier&lt;/emphasis&gt;. Chacun a eu un lancer.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a passé le ballon. Elle a visé le panier. Chacun a eu un lancer. Tu as passé, Mila. Bravo. Tu as visé le panier. Chacun un lancer.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1756,11 +1755,9 @@
 papa|Tu as passé, Mila.
 papa|Bravo.
 papa|Tu as visé le panier.
-enfant-f|Chacun un lancer.
-papa|C'est du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+enfant-f|Chacun un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1785,12 +1782,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le ballon. Mila essuie ses mains sur son pantalon. Le gilet rouge est encore sur le banc. Tu le prends ? Mila le prend. Il est doux. Tu bois une gorgée ? Oui. L'eau sent un peu le plastique. On a visé le panier. Oui, papa. On s'est passé le ballon. Chacun a eu un lancer. Bravo, ma grande. Tu as fait du bon travail. Le carré de soleil est plus petit. L'horloge fait encore tic.</t>
+          <t>Papa range le ballon. Mila essuie ses mains sur son pantalon. Le gilet rouge est encore sur le banc. Tu le prends ? Mila le prend. Il est doux. Tu bois une gorgée ? Oui. L'eau sent un peu le plastique. On a visé le panier. Oui, papa. On s'est passé le ballon. Chacun a eu un lancer. Bravo, ma grande. Le carré de soleil est plus petit. L'horloge fait encore tic.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa range le ballon. Klara essuie ses &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa range le ballon. Mila essuie ses mains sur son pantalon. Le gilet rouge est encore sur le banc. Tu le prends ? Mila le prend. Il est doux. Tu bois une gorgée ? Oui. L'eau sent un peu le plastique. On a visé le panier. Oui, papa. On s'est passé le ballon. Chacun a eu un lancer. Bravo, ma grande. Le carré de soleil est plus petit. L'horloge fait encore tic.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1939,7 +1936,6 @@
 enfant-f|On s'est passé le ballon.
 papa|Chacun a eu un lancer.
 papa|Bravo, ma grande.
-papa|Tu as fait du bon travail.
 narrateur|Le carré de soleil est plus petit.
 narrateur|L'horloge fait encore tic.</t>
         </is>
@@ -1973,12 +1969,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le gilet rouge est sur les épaules de Mila. J'ai passé. J'ai visé le panier. Bravo, Mila. L'histoire est finie.</t>
+          <t>Le gilet rouge est sur les épaules de Mila. J'ai passé. J'ai visé le panier. Bravo, Mila.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le gilet rouge est sur les épaules de Mila. J'ai passé. J'ai visé le panier. Bravo, Mila.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2116,11 +2112,9 @@
           <t>narrateur|Le gilet rouge est sur les épaules de Mila.
 enfant-f|J'ai passé.
 enfant-f|J'ai visé le panier.
-papa|Bravo, Mila.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo, Mila.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2139,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2184,6 +2178,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAS.001-07.xlsx
+++ b/stories/arbres/ATOM-JEU.BAS.001-07.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Klara, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
